--- a/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/التسويق_طالبات.xlsx
+++ b/المرفقات/المرشدين/توزيع فترات الارشاد/توزيع فترات الارشاد محدث/تحديث/نماذج_جاهزة_للرفع/التسويق_طالبات.xlsx
@@ -481,7 +481,7 @@
         <v>2</v>
       </c>
       <c r="B5" t="str">
-        <v>امل محمد احمد الثبيتي</v>
+        <v>بيان طايل غازي الحصيني</v>
       </c>
       <c r="C5" t="str">
         <v>204</v>
@@ -501,7 +501,7 @@
         <v>3</v>
       </c>
       <c r="B6" t="str">
-        <v>حنان ساعد مسعود المحياوي</v>
+        <v>اميره محمد علي احمد</v>
       </c>
       <c r="C6" t="str">
         <v>205</v>
@@ -561,7 +561,7 @@
         <v>6</v>
       </c>
       <c r="B9" t="str">
-        <v>امل محمد احمد الثبيتي</v>
+        <v>رحاب محمد مرحوم الحميدي</v>
       </c>
       <c r="C9" t="str">
         <v>204</v>
@@ -581,7 +581,7 @@
         <v>7</v>
       </c>
       <c r="B10" t="str">
-        <v>حنان ساعد مسعود المحياوي</v>
+        <v>خلود راغب عبدالسلام القطب</v>
       </c>
       <c r="C10" t="str">
         <v>205</v>
